--- a/public/sample2.xlsx
+++ b/public/sample2.xlsx
@@ -179,7 +179,7 @@
     <t>名前</t>
   </si>
   <si>
-    <t>要支援</t>
+    <t>学習支援</t>
   </si>
   <si>
     <t>田中 綾香</t>
@@ -436,7 +436,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>不登校気味</t>
+    <t>登校支援</t>
     <rPh sb="0" eb="5">
       <t>フトウコウギミ</t>
     </rPh>

--- a/public/sample2.xlsx
+++ b/public/sample2.xlsx
@@ -437,9 +437,6 @@
   </si>
   <si>
     <t>登校支援</t>
-    <rPh sb="0" eb="5">
-      <t>フトウコウギミ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>

--- a/public/sample2.xlsx
+++ b/public/sample2.xlsx
@@ -179,7 +179,7 @@
     <t>名前</t>
   </si>
   <si>
-    <t>要支援</t>
+    <t>学習支援</t>
   </si>
   <si>
     <t>田中 綾香</t>
@@ -436,10 +436,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>不登校気味</t>
-    <rPh sb="0" eb="5">
-      <t>フトウコウギミ</t>
-    </rPh>
+    <t>登校支援</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
